--- a/Config/Datas/shop.xlsx
+++ b/Config/Datas/shop.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,6 +562,21 @@
       <c r="D8" t="inlineStr">
         <is>
           <t>initial_orc_big</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VillageHerbalistShop</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>village_herbalist</t>
         </is>
       </c>
     </row>
@@ -576,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,6 +1028,72 @@
         <v>30</v>
       </c>
     </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>7001</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>flower_01</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>7002</v>
+      </c>
+      <c r="C14" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>herb_poultice</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>15</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>TaskStep,215,0,0,0,215_s2,0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>TaskStep,215,0,0,0,215_s2,0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
